--- a/src/test/resources/writer/style_if.xlsx
+++ b/src/test/resources/writer/style_if.xlsx
@@ -290,6 +290,7 @@
     <col min="3" max="3" width="35.18359375" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="32.19921875" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="18.875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="19.41015625" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="16.8671875" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="15.55859375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="20.953125" customWidth="true" bestFit="true"/>
